--- a/473/food/2026-02-03-sm.xlsx
+++ b/473/food/2026-02-03-sm.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>2026-02-03</t>
         </is>
       </c>
     </row>
